--- a/info.xlsx
+++ b/info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4_Learn\Python\devices_inspection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D830BC5D-D8B0-4906-B895-A8C2190D49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D2842B-7F4E-4EC6-BF78-0D2DF707AFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="1716" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="3210" windowWidth="16200" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1026,13 +1029,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="7" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.59765625" customWidth="1"/>
+    <col min="2" max="7" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1058,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
@@ -1101,7 +1104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>78</v>
       </c>
@@ -1124,7 +1127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>113</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>60</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1210,7 +1213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>135</v>
       </c>
@@ -1262,13 +1265,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E8D0F8-BD17-4983-B8A6-388FF13B2F1C}">
   <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="11" width="35.640625" customWidth="1"/>
-    <col min="12" max="13" width="20.5703125" customWidth="1"/>
+    <col min="1" max="11" width="35.6640625" customWidth="1"/>
+    <col min="12" max="13" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1304,7 +1307,7 @@
       </c>
       <c r="N1" s="3"/>
     </row>
-    <row r="2" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1362,7 +1365,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>112</v>
       </c>
@@ -1389,7 +1392,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1429,7 +1432,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1467,7 +1470,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
@@ -1496,7 +1499,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="4"/>
@@ -1569,7 +1572,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -1671,7 +1674,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="D19" s="2" t="s">
@@ -1751,7 +1754,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="D20" s="2" t="s">
@@ -1767,7 +1770,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1786,7 +1789,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1805,7 +1808,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -1823,7 +1826,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -1842,7 +1845,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -1869,7 +1872,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>163</v>
       </c>
@@ -1890,7 +1893,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>164</v>
       </c>
@@ -1911,7 +1914,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>171</v>
       </c>
@@ -1936,7 +1939,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>173</v>
       </c>
@@ -1951,7 +1954,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2" t="s">
@@ -1972,7 +1975,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
@@ -2001,7 +2004,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>111</v>
       </c>
@@ -2022,7 +2025,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -2049,7 +2052,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -2076,7 +2079,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -2097,7 +2100,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>31</v>
       </c>
@@ -2118,7 +2121,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>167</v>
       </c>
@@ -2139,7 +2142,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>168</v>
       </c>
@@ -2160,7 +2163,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>27</v>
       </c>
@@ -2189,7 +2192,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
@@ -2206,12 +2209,12 @@
       <c r="J40" s="2"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.4">
       <c r="C41" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>32</v>
       </c>
@@ -2240,68 +2243,68 @@
       <c r="J42" s="2"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.4">
       <c r="F48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="49" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="50" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="51" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L51" s="2"/>
     </row>
-    <row r="52" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="52" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="53" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="54" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="55" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="56" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="57" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="58" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="59" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="60" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="61" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="62" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="63" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="64" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="65" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="66" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="12:12" ht="15" x14ac:dyDescent="0.35">
+    <row r="67" spans="12:12" ht="15" x14ac:dyDescent="0.4">
       <c r="L67" s="2"/>
     </row>
   </sheetData>
